--- a/business_forms/041_dynamic_partner_leads_collection--business_forms.xlsx
+++ b/business_forms/041_dynamic_partner_leads_collection--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'CEO'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'entry_level'}</t>
+          <t>entry_level</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Entry Level'}</t>
+          <t>Entry Level</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'mid-level'}</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Mid-Level'}</t>
+          <t>Mid-Level</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'c-level'}</t>
+          <t>c-level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'C-Level'}</t>
+          <t>C-Level</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'intern'}</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Intern'}</t>
+          <t>Intern</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_"bachelor's"}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': "Bachelor's"}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_"master's"}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': "Master's"}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Doctorate'}</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Some college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'google_analytics'}</t>
+          <t>google_analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Google Analytics'}</t>
+          <t>Google Analytics</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'hubspot'}</t>
+          <t>hubspot</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'HubSpot'}</t>
+          <t>HubSpot</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'mandarin'}</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Mandarin'}</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
